--- a/data/trans_dic/IP21B-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP21B-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados</t>
+          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,22 +732,22 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,6</t>
+          <t>0,0; 76,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,58</t>
+          <t>0,0; 71,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,17 +757,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,12</t>
+          <t>0,0; 65,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,23</t>
+          <t>0,0; 65,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -778,7 +779,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,2</t>
+          <t>0,0; 48,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,71</t>
+          <t>0,0; 43,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,0</t>
+          <t>0,0; 78,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -881,44 +882,44 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,47</t>
+          <t>0,0; 59,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,92</t>
+          <t>0,0; 37,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,9; 41,7</t>
+          <t>0,0; 41,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,2</t>
+          <t>0,0; 43,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,15</t>
+          <t>0,0; 71,56</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,17 +997,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1016,12 +1017,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,21</t>
+          <t>0,0; 71,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,69</t>
+          <t>0,0; 38,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,91</t>
+          <t>0,0; 74,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,56</t>
+          <t>0,0; 80,0</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,24</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1146,52 +1147,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 80,15</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 67,16</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0; 77,15</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0; 26,42</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 73,32</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,89</t>
+          <t>0,0; 36,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,13</t>
+          <t>0,0; 61,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,03</t>
+          <t>0,0; 74,26</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1276,14 +1277,14 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 77,45</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1296,7 +1297,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1321,7 +1322,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,02</t>
+          <t>0,0; 71,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1338,7 +1339,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,52 +1417,52 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,14 +1472,14 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,17 +1557,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,35</t>
+          <t>0,0; 52,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,49</t>
+          <t>0,0; 53,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1576,42 +1577,42 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,73</t>
+          <t>0,0; 51,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,51</t>
+          <t>0,0; 63,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,93</t>
+          <t>0,0; 71,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,69</t>
+          <t>0,0; 41,2</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,52; 46,96</t>
+          <t>6,76; 45,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,8</t>
+          <t>0,0; 38,99</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,96</t>
+          <t>8,47; 72,55</t>
         </is>
       </c>
     </row>
@@ -1696,17 +1697,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,29</t>
+          <t>0,0; 81,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,3</t>
+          <t>0,0; 70,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,96</t>
+          <t>0,0; 83,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1716,17 +1717,17 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,29</t>
+          <t>0,0; 50,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,29</t>
+          <t>0,0; 60,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,87</t>
+          <t>0,0; 61,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1736,17 +1737,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,73</t>
+          <t>0,0; 47,17</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,1; 49,61</t>
+          <t>6,19; 50,4</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,8; 56,14</t>
+          <t>6,61; 52,93</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,51; 21,69</t>
+          <t>2,68; 22,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,22; 30,07</t>
+          <t>5,95; 30,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,84; 39,94</t>
+          <t>9,79; 39,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,57; 51,97</t>
+          <t>6,65; 52,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,29; 22,93</t>
+          <t>4,41; 24,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,1; 31,21</t>
+          <t>9,24; 30,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,93; 40,87</t>
+          <t>9,39; 41,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,28; 54,06</t>
+          <t>6,14; 52,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,38; 19,07</t>
+          <t>5,67; 19,61</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,75; 25,26</t>
+          <t>9,56; 25,0</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12,2; 33,65</t>
+          <t>12,76; 33,51</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,04; 43,04</t>
+          <t>12,21; 45,42</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1567</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1698</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3142</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3419</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1737</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2996</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4265</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2511</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1953</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2385</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 1970</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2372</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2173</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2663</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3843</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3842</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4511</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2607</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3047</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 1918</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3160</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2074</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3271</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2539</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2414</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2301</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 1755</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2183</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2897</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2143</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2390</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3740</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3615</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2067</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2129</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2022</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2673</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3457</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2985</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1608</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1411</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2925</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>1411</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2252</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4293</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3833</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 1674</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3696</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3287</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3453</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4320</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>898; 5992</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4021</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>550; 4706</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>1876</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2642</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2807</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3219</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2793</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3224</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2479</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 1204</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4116</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>577; 4694</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>521; 4171</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0; 1204</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2469</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>4353</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>4777</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>4069</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>6538</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>9171</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>5443</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>681; 5737</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1669; 8673</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2078; 8339</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>613; 4824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1462; 8152</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>3001; 9808</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1944; 8486</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>765; 6519</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>3318; 11486</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>5781; 15126</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5348; 14049</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>2647; 9845</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP21B-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP21B-Provincia-trans_dic.xlsx
@@ -742,12 +742,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,55</t>
+          <t>0,0; 81,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,22</t>
+          <t>0,0; 70,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,34</t>
+          <t>0,0; 66,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,64</t>
+          <t>0,0; 60,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,32</t>
+          <t>0,0; 53,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,91</t>
+          <t>0,0; 80,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,9</t>
+          <t>0,0; 51,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,73</t>
+          <t>0,0; 37,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,25</t>
+          <t>5,9; 41,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,52</t>
+          <t>0,0; 43,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,56</t>
+          <t>0,0; 71,06</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,13</t>
+          <t>0,0; 40,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,84</t>
+          <t>0,0; 78,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,0</t>
+          <t>0,0; 74,12</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,77</t>
+          <t>0,0; 35,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,63</t>
+          <t>0,0; 61,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,26</t>
+          <t>0,0; 74,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,0</t>
+          <t>0,0; 82,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,73</t>
+          <t>0,0; 72,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,77</t>
+          <t>0,0; 52,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,33</t>
+          <t>0,0; 48,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,37</t>
+          <t>0,0; 51,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,99</t>
+          <t>0,0; 63,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1592,27 +1592,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,73</t>
+          <t>0,0; 72,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,2</t>
+          <t>0,0; 40,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,76; 45,14</t>
+          <t>5,33; 47,52</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,99</t>
+          <t>0,0; 40,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,47; 72,55</t>
+          <t>8,79; 73,39</t>
         </is>
       </c>
     </row>
@@ -1697,17 +1697,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,4</t>
+          <t>0,0; 74,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,25</t>
+          <t>0,0; 68,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,25</t>
+          <t>0,0; 83,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1717,17 +1717,17 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,96</t>
+          <t>0,0; 51,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,63</t>
+          <t>0,0; 60,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,79</t>
+          <t>0,0; 61,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1737,17 +1737,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,17</t>
+          <t>0,0; 46,06</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,19; 50,4</t>
+          <t>6,11; 48,33</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,61; 52,93</t>
+          <t>6,53; 50,55</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,68; 22,58</t>
+          <t>2,29; 20,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,95; 30,95</t>
+          <t>5,56; 29,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,79; 39,28</t>
+          <t>10,16; 40,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,65; 52,35</t>
+          <t>6,65; 51,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,41; 24,59</t>
+          <t>5,66; 22,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,24; 30,2</t>
+          <t>8,27; 30,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,39; 41,0</t>
+          <t>7,71; 39,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,14; 52,31</t>
+          <t>7,29; 55,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,67; 19,61</t>
+          <t>5,66; 18,81</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,56; 25,0</t>
+          <t>9,62; 25,44</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12,76; 33,51</t>
+          <t>12,56; 33,94</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,21; 45,42</t>
+          <t>11,03; 45,71</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3142</t>
+          <t>0; 3335</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3419</t>
+          <t>0; 3397</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2254,12 +2254,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2996</t>
+          <t>0; 3032</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4265</t>
+          <t>0; 3955</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2385</t>
+          <t>0; 2644</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2372</t>
+          <t>0; 2405</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3843</t>
+          <t>0; 3272</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2457,22 +2457,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3842</t>
+          <t>0; 3803</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4511</t>
+          <t>645; 4560</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2607</t>
+          <t>0; 2634</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 3047</t>
+          <t>0; 3026</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3271</t>
+          <t>0; 3506</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2675,12 +2675,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2539</t>
+          <t>0; 2663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2414</t>
+          <t>0; 2236</t>
         </is>
       </c>
     </row>
@@ -2873,17 +2873,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2390</t>
+          <t>0; 2328</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 3740</t>
+          <t>0; 3738</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 3615</t>
+          <t>0; 3625</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2673</t>
+          <t>0; 2742</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 3457</t>
+          <t>0; 3473</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3462,12 +3462,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4293</t>
+          <t>0; 4285</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3833</t>
+          <t>0; 3473</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3696</t>
+          <t>0; 3705</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3287</t>
+          <t>0; 3274</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3492,27 +3492,27 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3453</t>
+          <t>0; 3483</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4320</t>
+          <t>0; 4205</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>898; 5992</t>
+          <t>708; 6307</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 4021</t>
+          <t>0; 4149</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>550; 4706</t>
+          <t>570; 4761</t>
         </is>
       </c>
     </row>
@@ -3665,17 +3665,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 2642</t>
+          <t>0; 2418</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2807</t>
+          <t>0; 2729</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3219</t>
+          <t>0; 3240</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,17 +3685,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 2793</t>
+          <t>0; 2798</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 3224</t>
+          <t>0; 3206</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 2479</t>
+          <t>0; 2456</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3705,17 +3705,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 4116</t>
+          <t>0; 4019</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>577; 4694</t>
+          <t>569; 4501</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>521; 4171</t>
+          <t>514; 3983</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>681; 5737</t>
+          <t>583; 5282</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1669; 8673</t>
+          <t>1559; 8175</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2078; 8339</t>
+          <t>2157; 8692</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>613; 4824</t>
+          <t>613; 4782</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1462; 8152</t>
+          <t>1877; 7536</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3001; 9808</t>
+          <t>2687; 9777</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1944; 8486</t>
+          <t>1597; 8186</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>765; 6519</t>
+          <t>908; 6874</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3318; 11486</t>
+          <t>3316; 11013</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5781; 15126</t>
+          <t>5821; 15389</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5348; 14049</t>
+          <t>5266; 14230</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2647; 9845</t>
+          <t>2390; 9907</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP21B-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP21B-Provincia-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -654,44 +654,44 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>16,25%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18,57%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>50,19%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>39,8%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,57%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>53,27%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>14,55%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 76,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 65,58</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,77</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,87</t>
+          <t>0,0; 62,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,5</t>
+          <t>0,0; 84,31</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12,82%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20,38%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>11,68%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>14,27%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>20,09%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>38,24%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>12,82%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>20,38%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,56</t>
+          <t>0,0; 50,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,55</t>
+          <t>0,0; 60,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 48,2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 57,71</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 80,0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 50,76</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 51,0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,35</t>
+          <t>0,0; 36,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,9; 41,69</t>
+          <t>5,9; 41,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,96</t>
+          <t>0,0; 48,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,06</t>
+          <t>0,0; 78,97</t>
         </is>
       </c>
     </row>
@@ -929,29 +929,29 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28,48%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32,3%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30,73%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>28,48%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -959,24 +959,24 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>32,63%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>14,58%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>14,58%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>19,75%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 71,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,37 +1007,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 71,97</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,87</t>
+          <t>0,0; 37,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,49</t>
+          <t>0,0; 78,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,12</t>
+          <t>0,0; 79,34</t>
         </is>
       </c>
     </row>
@@ -1069,37 +1069,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15,82%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33,9%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>22,89%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>37,38%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>27,87%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1137,34 +1137,34 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 73,32</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 75,24</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 80,15</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 67,16</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,82</t>
+          <t>0,0; 43,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,59</t>
+          <t>0,0; 62,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,46</t>
+          <t>0,0; 74,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1209,32 +1209,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>25,11%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>26,69%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>33,33%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>25,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 75,16</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,16</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,08</t>
+          <t>0,0; 80,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,07</t>
+          <t>0,0; 72,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1359,27 +1359,27 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20,09%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25,64%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>28,67%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>19,76%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>19,63%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>49,12%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>20,09%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 54,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,67</t>
+          <t>0,0; 63,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>0,0; 82,07</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 51,35</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 49,49</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 51,49</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 63,73</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 72,37</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,11</t>
+          <t>0,0; 40,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,33; 47,52</t>
+          <t>9,52; 46,96</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,23</t>
+          <t>0,0; 40,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,79; 73,39</t>
+          <t>0,0; 71,42</t>
         </is>
       </c>
     </row>
@@ -1629,44 +1629,44 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12,78%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22,66%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13,67%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>74,65%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>20,14%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>18,37%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>34,34%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>12,78%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>22,66%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>13,67%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>70,24%</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
           <t>15,52%</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>74,65%</t>
         </is>
       </c>
     </row>
@@ -1697,57 +1697,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,48</t>
+          <t>0,0; 51,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,3</t>
+          <t>0,0; 60,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,79</t>
+          <t>0,0; 62,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,06</t>
+          <t>0,0; 77,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,29</t>
+          <t>0,0; 70,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,22</t>
+          <t>0,0; 71,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,06</t>
+          <t>0,0; 44,73</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,11; 48,33</t>
+          <t>6,1; 49,61</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,53; 50,55</t>
+          <t>6,8; 56,14</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>18,03%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>21,23%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>26,48%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>9,72%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>15,53%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>22,51%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>24,34%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>18,03%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>21,23%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,29; 20,79</t>
+          <t>4,29; 22,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,56; 29,17</t>
+          <t>8,1; 31,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,16; 40,95</t>
+          <t>7,93; 40,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,65; 51,89</t>
+          <t>7,75; 55,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,66; 22,73</t>
+          <t>2,51; 21,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,27; 30,1</t>
+          <t>5,22; 30,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,71; 39,55</t>
+          <t>9,84; 39,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,29; 55,16</t>
+          <t>7,54; 55,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,66; 18,81</t>
+          <t>5,38; 19,07</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,62; 25,44</t>
+          <t>9,75; 25,26</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12,56; 33,94</t>
+          <t>12,2; 33,65</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,03; 45,71</t>
+          <t>11,63; 44,95</t>
         </is>
       </c>
     </row>
@@ -1951,13 +1951,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2098,17 +2098,17 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2146,49 +2146,49 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>676</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
           <t>1567</t>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>743</t>
         </is>
       </c>
     </row>
@@ -2214,37 +2214,37 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3144</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0; 3148</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1480</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>0; 1698</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3335</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3397</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1737</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3955</t>
+          <t>0; 4044</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2511</t>
+          <t>0; 2160</t>
         </is>
       </c>
     </row>
@@ -2286,37 +2286,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1308</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>576</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>645</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>604</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>831</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1308</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>870</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>870</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2644</t>
+          <t>0; 2663</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1970</t>
+          <t>0; 3880</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2380</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2610</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>0; 2405</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 2173</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0; 2663</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3272</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2259</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3803</t>
+          <t>0; 3760</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>645; 4560</t>
+          <t>645; 4561</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2634</t>
+          <t>0; 2887</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 3026</t>
+          <t>0; 3188</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2499,32 +2499,32 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2567,52 +2567,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>1250</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>670</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1250</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>627</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3126</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2635,17 +2635,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2074</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1918</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3160</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2655,17 +2655,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2074</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1921</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3506</t>
+          <t>0; 3233</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2675,12 +2675,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2663</t>
+          <t>0; 2677</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2236</t>
+          <t>0; 2246</t>
         </is>
       </c>
     </row>
@@ -2697,27 +2697,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -2765,37 +2765,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>759</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2833,37 +2833,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2301</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>0; 3163</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2143</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 1731</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>0; 1755</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0; 2183</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0; 2897</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2143</t>
+          <t>0; 2724</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2328</t>
+          <t>0; 2852</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 3738</t>
+          <t>0; 3771</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 3625</t>
+          <t>0; 3604</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2905,27 +2905,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2973,32 +2973,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>710</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2067</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>0; 2022</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2669</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>0; 2129</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0; 2022</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -3081,12 +3081,12 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2742</t>
+          <t>0; 2673</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 3473</t>
+          <t>0; 3471</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,49 +3389,49 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>1608</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>1411</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>822</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>1445</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1430</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1445</t>
-        </is>
-      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t>2925</t>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>2223</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3938</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4285</t>
+          <t>0; 3263</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3473</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 1674</t>
+          <t>0; 3902</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3705</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3274</t>
+          <t>0; 4178</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3557</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3483</t>
+          <t>0; 1595</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4205</t>
+          <t>0; 4265</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>708; 6307</t>
+          <t>1263; 6234</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 4149</t>
+          <t>0; 4207</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>570; 4761</t>
+          <t>0; 4535</t>
         </is>
       </c>
     </row>
@@ -3534,37 +3534,37 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,44 +3597,44 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1205</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>654</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>734</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>1328</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1205</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>846</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t>1354</t>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>894</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 2418</t>
+          <t>0; 2811</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2729</t>
+          <t>0; 3206</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3240</t>
+          <t>0; 2522</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1197</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 2798</t>
+          <t>0; 2509</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 3206</t>
+          <t>0; 2809</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 2456</t>
+          <t>0; 2783</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 1204</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 4019</t>
+          <t>0; 3903</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>569; 4501</t>
+          <t>568; 4621</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>514; 3983</t>
+          <t>536; 4423</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 1204</t>
+          <t>0; 1197</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>4069</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2999</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>2469</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>4353</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>4777</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2243</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>4069</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>5854</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>4394</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5356</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>583; 5282</t>
+          <t>1421; 7603</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1559; 8175</t>
+          <t>2630; 10136</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2157; 8692</t>
+          <t>1642; 8458</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>613; 4782</t>
+          <t>877; 6332</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1877; 7536</t>
+          <t>638; 5511</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2687; 9777</t>
+          <t>1463; 8427</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1597; 8186</t>
+          <t>2089; 8479</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>908; 6874</t>
+          <t>666; 4896</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3316; 11013</t>
+          <t>3148; 11170</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5821; 15389</t>
+          <t>5902; 15280</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5266; 14230</t>
+          <t>5116; 14107</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2390; 9907</t>
+          <t>2344; 9061</t>
         </is>
       </c>
     </row>
